--- a/output/pdf_financials_xlsx/NIRV.X.xlsx
+++ b/output/pdf_financials_xlsx/NIRV.X.xlsx
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.11228</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.316873</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.5595560000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.5746790000000001</v>
       </c>
     </row>
     <row r="93">
@@ -3466,7 +3466,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3892,7 +3896,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4154,7 +4162,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.11228</v>
       </c>

--- a/output/pdf_financials_xlsx/NIRV.X.xlsx
+++ b/output/pdf_financials_xlsx/NIRV.X.xlsx
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.012341</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5.4e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.656673</v>
+        <v>-5.669014</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.491464</v>
+        <v>-1.491518</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.873363</v>
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.656673</v>
+        <v>-5.669014</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.39982</v>
+        <v>-1.399874</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.8550489999999999</v>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.035769</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.012492</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001913</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002677</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.035769</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.012492</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001913</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002677</v>
       </c>
     </row>
     <row r="37">
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.143935</v>
+        <v>0.108166</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.068568</v>
+        <v>0.056076</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">

--- a/output/pdf_financials_xlsx/NIRV.X.xlsx
+++ b/output/pdf_financials_xlsx/NIRV.X.xlsx
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.091645</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.091644</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.669014</v>
+        <v>-5.577369</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.399874</v>
@@ -1720,16 +1720,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.028769</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.025319</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="68">
@@ -2339,10 +2339,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-5.656673</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-1.491464</v>
@@ -2360,10 +2358,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2381,10 +2377,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -2402,10 +2396,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2423,10 +2415,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.009076000000000001</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0.054771</v>
@@ -2444,10 +2434,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.101926</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.053789</v>
@@ -2465,10 +2453,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -2486,10 +2472,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.111002</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.10856</v>
@@ -2507,10 +2491,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.204593</v>
@@ -2528,10 +2510,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -2549,10 +2529,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -2570,10 +2548,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -2591,10 +2567,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2612,10 +2586,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2633,10 +2605,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -2654,10 +2624,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -2675,10 +2643,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2696,10 +2662,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -2717,10 +2681,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -2738,10 +2700,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -2759,10 +2719,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.100837</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0</v>
@@ -2780,10 +2738,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -2801,10 +2757,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -2822,10 +2776,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -2843,10 +2795,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2864,10 +2814,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2885,10 +2833,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2906,10 +2852,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -2954,10 +2898,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -2975,10 +2917,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.002267</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.309934</v>
@@ -2996,10 +2936,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.624529</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.035769</v>
@@ -3017,10 +2955,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -3038,10 +2974,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.58876</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.023277</v>
@@ -3059,10 +2993,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.035769</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.012492</v>
@@ -3080,10 +3012,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3101,10 +3031,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.49019</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.333211</v>
@@ -3127,7 +3055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4383,10 +4311,8 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="5" t="n">
+        <v>-5.656673</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>-1.491464</v>
@@ -4453,10 +4379,8 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="5" t="n">
+        <v>0.091645</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>0.091644</v>
@@ -4593,10 +4517,8 @@
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="5" t="n">
+        <v>0.007972</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>-0.002681</v>
@@ -4629,10 +4551,8 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" s="5" t="n">
+        <v>-0.009076000000000001</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>0.054771</v>
@@ -4667,10 +4587,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" s="5" t="n">
+        <v>-0.101926</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>0.053789</v>
@@ -4699,10 +4617,8 @@
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="5" t="n">
+        <v>0.380316</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>0.270105</v>
@@ -4735,10 +4651,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="5" t="n">
+        <v>-0.49019</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>-0.333211</v>
@@ -4801,10 +4715,8 @@
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="5" t="n">
+        <v>0.002267</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>0.05</v>
@@ -4837,10 +4749,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>0.002267</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0.309934</v>
@@ -4873,10 +4783,8 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="5" t="n">
+        <v>-0.58876</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>-0.023277</v>
@@ -4909,10 +4817,8 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="5" t="n">
+        <v>0.624529</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0.035769</v>
@@ -4945,10 +4851,8 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" s="5" t="n">
+        <v>0.035769</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>0.012492</v>
@@ -5071,62 +4975,68 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Accounting and audit $</t>
+          <t>Accrued interest income</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.057722</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>0.055743</v>
+        <v>-0.012341</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Consulting 7</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.14</v>
+        <v>4.490415</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -5137,36 +5047,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Depreciation 5</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Provision for doubtful receivables</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>0.319478</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n">
-        <v>0.018314</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5177,56 +5083,58 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Loan receivable due from related party</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0.00657</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.05039</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.001945</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>0.00024</v>
+        <v>-0.207</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Legal fees 7</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5239,40 +5147,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>0.010869</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>0.020001</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loan interest 7</t>
+          <t>Cash acquired on RTO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.008397</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.000665</v>
+      <c r="E60" s="5" t="n">
+        <v>0.106163</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -5283,35 +5197,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Management fees 7</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>0.193846</v>
+        <v>-0.100837</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -5327,25 +5247,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Marketing and promotion</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounting and audit $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>0.039091</v>
+        <v>0.035</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.248474</v>
+        <v>0.037</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.057722</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.04756</v>
+        <v>0.055743</v>
       </c>
     </row>
     <row r="63">
@@ -5361,25 +5277,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Consulting 7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.024518</v>
+        <v>0.178</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.008479</v>
+        <v>0.159</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.010908</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>0.007671</v>
+        <v>0.14</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -5395,12 +5313,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Research and development 7, 10</t>
+          <t>Depreciation 5</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5414,7 +5332,7 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.115221</v>
+        <v>0.018314</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5435,23 +5353,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Share-based payments 7, 9</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.00657</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.204593</v>
+        <v>0.05039</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.178683</v>
+        <v>0.001945</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.015123</v>
+        <v>0.00024</v>
       </c>
     </row>
     <row r="66">
@@ -5467,7 +5387,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Legal fees 7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5475,17 +5395,21 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>0.007549</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.024611</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.027425</v>
+        <v>0.010869</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.025737</v>
+        <v>0.020001</v>
       </c>
     </row>
     <row r="67">
@@ -5501,22 +5425,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0.001211</v>
+          <t>Loan interest 7</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.006482</v>
+        <v>0.008397</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.000425</v>
+        <v>0.000665</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5537,21 +5459,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Loss before items below</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Management fees 7</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
-        <v>-0.859121</v>
+        <v>0.0375</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-1.258856</v>
+        <v>0.21</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.744677</v>
+        <v>0.18</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>-0.365921</v>
+        <v>0.193846</v>
       </c>
     </row>
     <row r="69">
@@ -5567,27 +5493,25 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 7, 8</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Marketing and promotion</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.039091</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.248474</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0025</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0.04756</v>
       </c>
     </row>
     <row r="70">
@@ -5603,27 +5527,25 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Impairment loss on intangible asset 5</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0.024518</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0.008479</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.156686</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010908</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0.007671</v>
       </c>
     </row>
     <row r="71">
@@ -5639,25 +5561,31 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Research and development 7, 10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>-5.656673</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>-1.491464</v>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.873363</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>-0.365921</v>
+        <v>0.115221</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -5668,12 +5596,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Equity holders of Nirvana Life Sciences Inc.</t>
+          <t>Share-based payments 7, 9</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5683,13 +5611,13 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-1.487302</v>
+        <v>0.204593</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.871824</v>
+        <v>0.178683</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-0.365918</v>
+        <v>0.015123</v>
       </c>
     </row>
     <row r="73">
@@ -5700,30 +5628,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Non-controlling interests 11</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0.002468</v>
+        <v>0.007549</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.004162</v>
+        <v>0.024611</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.001539</v>
+        <v>0.027425</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.025737</v>
       </c>
     </row>
     <row r="74">
@@ -5734,30 +5662,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>-1.6e-07</v>
+        <v>0.001211</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.006482</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-1.9e-07</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>-8e-08</v>
+        <v>0.000425</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -5768,30 +5698,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Loss before items below</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>36.520229</v>
+        <v>-0.859121</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>33.94421</v>
+        <v>-1.258856</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>4.670917</v>
+        <v>-0.744677</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>4.823301</v>
+        <v>-0.365921</v>
       </c>
     </row>
     <row r="76">
@@ -5807,24 +5733,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Consulting 8</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 7, 8</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>0.159</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.14</v>
+        <v>0.028</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5845,24 +5769,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Depreciation 5, 6</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Impairment loss on intangible asset 5</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F77" s="5" t="n">
-        <v>0.091644</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.018314</v>
+        <v>-0.156686</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5883,29 +5805,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Legal fees 8</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-5.656673</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.010566</v>
+        <v>-1.491464</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.010869</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.873363</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>-0.365921</v>
       </c>
     </row>
     <row r="79">
@@ -5916,12 +5834,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Loan interest 8</t>
+          <t>Equity holders of Nirvana Life Sciences Inc.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -5931,15 +5849,13 @@
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.008397</v>
+        <v>-1.487302</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.000665</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.871824</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>-0.365918</v>
       </c>
     </row>
     <row r="80">
@@ -5950,34 +5866,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Management fees 8</t>
+          <t>Non-controlling interests 11</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0.002468</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.21</v>
+        <v>0.004162</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001539</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>3e-06</v>
       </c>
     </row>
     <row r="81">
@@ -5988,34 +5900,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0.030839</v>
+        <v>-1.6e-07</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.07344000000000001</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-1.9e-07</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>-8e-08</v>
       </c>
     </row>
     <row r="82">
@@ -6026,34 +5934,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.07249700000000001</v>
+        <v>36.520229</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.034253</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>33.94421</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>4.670917</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>4.823301</v>
       </c>
     </row>
     <row r="83">
@@ -6069,12 +5973,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Research and development 8, 11</t>
+          <t>Consulting 8</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6083,10 +5987,10 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.091527</v>
+        <v>0.159</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.115221</v>
+        <v>0.14</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6107,20 +6011,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Share-based payments 8, 10</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Depreciation 5, 6</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.204593</v>
+        <v>0.091644</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.178683</v>
+        <v>0.018314</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6141,24 +6049,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Legal fees 8</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0.012341</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>5.4e-05</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010566</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.010869</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6179,7 +6087,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 8, 9</t>
+          <t>Loan interest 8</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6189,10 +6097,10 @@
         </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.018338</v>
+        <v>0.008397</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.028</v>
+        <v>0.000665</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6213,22 +6121,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Impairment loss on equipment 5</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Management fees 8</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.251</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.21</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.18</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6249,22 +6159,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Impairment loss on intangible asset 6</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>-0.156686</v>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.030839</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.07344000000000001</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -6280,29 +6192,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Non-controlling interests 12</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.07249700000000001</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.004162</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0.001539</v>
+        <v>0.034253</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -6318,25 +6230,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Total (161,592) 150,000 248,742 109,934 204,593 (939,787) 210,066 112,000 175,000 178,683 (873,363) deficiency</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Research and development 8, 11</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-1.137401</v>
+        <v>0.091527</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-1.491464</v>
+        <v>0.115221</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6352,12 +6268,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Attributable to total</t>
+          <t>Share-based payments 8, 10</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -6367,10 +6283,10 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>-0.003439</v>
+        <v>0.204593</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.004162</v>
+        <v>0.178683</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6386,25 +6302,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Non-controlling interests</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Deficit - - - - - - - - (871,824) statements. (6,257,738) (1,487,302)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0.012341</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-8.616864</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-7.74504</v>
+        <v>5.4e-05</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6425,24 +6345,20 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>0.091645</v>
+          <t>Gain on debt settlement 8, 9</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.091644</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018338</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.028</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6463,19 +6379,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>0.013887</v>
+          <t>Impairment loss on equipment 5</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.010566</v>
+        <v>-0.251</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6501,24 +6415,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Research and development 7, 11</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>0.320814</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>0.091527</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Impairment loss on intangible asset 6</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.156686</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6534,27 +6446,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 8</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Non-controlling interests 12</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.018338</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004162</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.001539</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6570,12 +6484,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Impairment loss on equipment</t>
+          <t>Total (161,592) 150,000 248,742 109,934 204,593 (939,787) 210,066 112,000 175,000 178,683 (873,363) deficiency</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -6585,12 +6499,10 @@
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.137401</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-1.491464</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6606,27 +6518,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Listing expense 4</t>
+          <t>Attributable to total</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" s="5" t="n">
-        <v>-4.490415</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>-0.003439</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-0.004162</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6642,27 +6552,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-controlling interests</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Provision for doubtful receivables 7</t>
+          <t>Deficit - - - - - - - - (871,824) statements. (6,257,738) (1,487,302)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>-0.319478</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>-8.616864</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-7.74504</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6678,27 +6586,285 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0.091645</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.091644</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.013887</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.010566</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Research and development 7, 11</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0.320814</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.091527</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gain on debt settlement 8</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.018338</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Impairment loss on equipment</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Listing expense 4</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>-4.490415</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Provision for doubtful receivables 7</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>-0.319478</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>Attributable to</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Equity holders of Nirvana Life Sciences Inc. 4</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
         <v>-5.654205</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F107" s="5" t="n">
         <v>-1.487302</v>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
